--- a/data/trans_orig/IP31KM02_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36028</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30188</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41968</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>30755</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19855</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38708</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>57,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37810</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43515</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>68565</t>
+          <t>63741</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78969</t>
+          <t>72202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22944</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43478</t>
+          <t>35879</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57014</t>
+          <t>44460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>271742</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>247216</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>291988</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>58,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>53,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>62,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>246613</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>200474</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>270069</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>44,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>59,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>285657</t>
+          <t>250404</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>258594</t>
+          <t>232232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>310875</t>
+          <t>264762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>532269</t>
+          <t>522147</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>477428</t>
+          <t>493327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>565741</t>
+          <t>551751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>205219</t>
+          <t>194681</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181763</t>
+          <t>174435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251358</t>
+          <t>219207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>219593</t>
+          <t>174262</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194375</t>
+          <t>159904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246656</t>
+          <t>192434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>424813</t>
+          <t>368943</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391341</t>
+          <t>339339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>479654</t>
+          <t>397763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>103064</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>92141</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>112916</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>61,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>55,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87536</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>77361</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>96179</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>59,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>110153</t>
+          <t>89205</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96709</t>
+          <t>78986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122063</t>
+          <t>98538</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>197689</t>
+          <t>192269</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182634</t>
+          <t>177489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212772</t>
+          <t>207890</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63622</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53770</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74545</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>58650</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>50007</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68825</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>40,12%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70986</t>
+          <t>57935</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59076</t>
+          <t>48602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84430</t>
+          <t>68154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>129635</t>
+          <t>121556</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114552</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144690</t>
+          <t>136336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>410834</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>384652</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>434676</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>56,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>63,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>543</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>364904</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>317995</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>393730</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>367322</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>403613</t>
+          <t>346671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>461505</t>
+          <t>386522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>798524</t>
+          <t>778156</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>744857</t>
+          <t>744314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834060</t>
+          <t>810592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>275990</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>252148</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>302172</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>286813</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>257987</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>333722</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>311113</t>
+          <t>250389</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283228</t>
+          <t>231189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>341120</t>
+          <t>271040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>597926</t>
+          <t>526379</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562390</t>
+          <t>493943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>651593</t>
+          <t>560221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
